--- a/25-경기철도-용인시-보고서.xlsx
+++ b/25-경기철도-용인시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T126"/>
+  <dimension ref="A1:T127"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8344,9 +8344,71 @@
         <v/>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>26-11</v>
+      </c>
+      <c r="B127" t="str">
+        <v>신수로</v>
+      </c>
+      <c r="C127" t="str">
+        <v>26-용인시-11</v>
+      </c>
+      <c r="D127" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E127" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F127" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G127" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H127" t="str">
+        <v>-</v>
+      </c>
+      <c r="I127" t="str">
+        <v>0</v>
+      </c>
+      <c r="J127" t="str">
+        <v>3</v>
+      </c>
+      <c r="K127" t="str">
+        <v>0</v>
+      </c>
+      <c r="L127" t="str">
+        <v>1</v>
+      </c>
+      <c r="M127" t="str">
+        <v>0</v>
+      </c>
+      <c r="N127" t="str">
+        <v>4</v>
+      </c>
+      <c r="O127" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P127" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q127" t="str">
+        <v>풍덕천동860-6</v>
+      </c>
+      <c r="R127" t="str">
+        <v/>
+      </c>
+      <c r="S127" t="str">
+        <v>제네시스_수지 앞 도로(풍덕천로197번길11-2)</v>
+      </c>
+      <c r="T127" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T126"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T127"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-용인시-보고서.xlsx
+++ b/25-경기철도-용인시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T127"/>
+  <dimension ref="A1:T132"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8403,12 +8403,322 @@
         <v>제네시스_수지 앞 도로(풍덕천로197번길11-2)</v>
       </c>
       <c r="T127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>26-12</v>
+      </c>
+      <c r="B128" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C128" t="str">
+        <v>26-용인시-12</v>
+      </c>
+      <c r="D128" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E128" t="str">
+        <v>양호</v>
+      </c>
+      <c r="F128" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G128" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H128" t="str">
+        <v>-</v>
+      </c>
+      <c r="I128" t="str">
+        <v>0</v>
+      </c>
+      <c r="J128" t="str">
+        <v>0</v>
+      </c>
+      <c r="K128" t="str">
+        <v>0</v>
+      </c>
+      <c r="L128" t="str">
+        <v>1</v>
+      </c>
+      <c r="M128" t="str">
+        <v>0</v>
+      </c>
+      <c r="N128" t="str">
+        <v>1</v>
+      </c>
+      <c r="O128" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P128" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q128" t="str">
+        <v>풍덕천동740-9</v>
+      </c>
+      <c r="R128" t="str">
+        <v/>
+      </c>
+      <c r="S128" t="str">
+        <v>돌담집 앞 도로(풍덕천로197번길3-2)</v>
+      </c>
+      <c r="T128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>26-13</v>
+      </c>
+      <c r="B129" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C129" t="str">
+        <v>26-용인시-13</v>
+      </c>
+      <c r="D129" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E129" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F129" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G129" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H129" t="str">
+        <v>-</v>
+      </c>
+      <c r="I129" t="str">
+        <v>0</v>
+      </c>
+      <c r="J129" t="str">
+        <v>3</v>
+      </c>
+      <c r="K129" t="str">
+        <v>0</v>
+      </c>
+      <c r="L129" t="str">
+        <v>1</v>
+      </c>
+      <c r="M129" t="str">
+        <v>0</v>
+      </c>
+      <c r="N129" t="str">
+        <v>4</v>
+      </c>
+      <c r="O129" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P129" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q129" t="str">
+        <v>풍덕천동740-9</v>
+      </c>
+      <c r="R129" t="str">
+        <v/>
+      </c>
+      <c r="S129" t="str">
+        <v>돌담집 앞 삼거리(풍덕천로197번길3-2)</v>
+      </c>
+      <c r="T129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>26-14</v>
+      </c>
+      <c r="B130" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C130" t="str">
+        <v>26-용인시-14</v>
+      </c>
+      <c r="D130" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E130" t="str">
+        <v>양호</v>
+      </c>
+      <c r="F130" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G130" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H130" t="str">
+        <v>-</v>
+      </c>
+      <c r="I130" t="str">
+        <v>0</v>
+      </c>
+      <c r="J130" t="str">
+        <v>0</v>
+      </c>
+      <c r="K130" t="str">
+        <v>0</v>
+      </c>
+      <c r="L130" t="str">
+        <v>1</v>
+      </c>
+      <c r="M130" t="str">
+        <v>0</v>
+      </c>
+      <c r="N130" t="str">
+        <v>1</v>
+      </c>
+      <c r="O130" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P130" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q130" t="str">
+        <v>풍덕천동742-8</v>
+      </c>
+      <c r="R130" t="str">
+        <v/>
+      </c>
+      <c r="S130" t="str">
+        <v>샤인노래방 앞 도로(풍덕천로197번길1)</v>
+      </c>
+      <c r="T130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>26-15</v>
+      </c>
+      <c r="B131" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C131" t="str">
+        <v>26-용인시-15</v>
+      </c>
+      <c r="D131" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E131" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F131" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G131" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H131" t="str">
+        <v>-</v>
+      </c>
+      <c r="I131" t="str">
+        <v>0</v>
+      </c>
+      <c r="J131" t="str">
+        <v>3</v>
+      </c>
+      <c r="K131" t="str">
+        <v>0</v>
+      </c>
+      <c r="L131" t="str">
+        <v>1</v>
+      </c>
+      <c r="M131" t="str">
+        <v>0</v>
+      </c>
+      <c r="N131" t="str">
+        <v>4</v>
+      </c>
+      <c r="O131" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P131" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q131" t="str">
+        <v>풍덕천동742</v>
+      </c>
+      <c r="R131" t="str">
+        <v/>
+      </c>
+      <c r="S131" t="str">
+        <v>덕윤프라자 앞 도로(풍덕천로191)</v>
+      </c>
+      <c r="T131" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>26-16</v>
+      </c>
+      <c r="B132" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C132" t="str">
+        <v>26-용인시-15</v>
+      </c>
+      <c r="D132" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E132" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F132" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G132" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H132" t="str">
+        <v>-</v>
+      </c>
+      <c r="I132" t="str">
+        <v>0</v>
+      </c>
+      <c r="J132" t="str">
+        <v>3</v>
+      </c>
+      <c r="K132" t="str">
+        <v>0</v>
+      </c>
+      <c r="L132" t="str">
+        <v>1</v>
+      </c>
+      <c r="M132" t="str">
+        <v>0</v>
+      </c>
+      <c r="N132" t="str">
+        <v>4</v>
+      </c>
+      <c r="O132" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P132" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q132" t="str">
+        <v>풍덕천동735-7</v>
+      </c>
+      <c r="R132" t="str">
+        <v/>
+      </c>
+      <c r="S132" t="str">
+        <v>삼정빌딩 앞 도로(풍덕천로187-1)</v>
+      </c>
+      <c r="T132" t="str">
         <v>현장확인필요</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T127"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T132"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-용인시-보고서.xlsx
+++ b/25-경기철도-용인시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T132"/>
+  <dimension ref="A1:T138"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8651,7 +8651,7 @@
         <v>덕윤프라자 앞 도로(풍덕천로191)</v>
       </c>
       <c r="T131" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="132">
@@ -8662,7 +8662,7 @@
         <v>풍덕천로</v>
       </c>
       <c r="C132" t="str">
-        <v>26-용인시-15</v>
+        <v>26-용인시-16</v>
       </c>
       <c r="D132" t="str">
         <v>양호</v>
@@ -8713,12 +8713,384 @@
         <v>삼정빌딩 앞 도로(풍덕천로187-1)</v>
       </c>
       <c r="T132" t="str">
-        <v>현장확인필요</v>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>26-17</v>
+      </c>
+      <c r="B133" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C133" t="str">
+        <v>26-용인시-17</v>
+      </c>
+      <c r="D133" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E133" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F133" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G133" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H133" t="str">
+        <v>-</v>
+      </c>
+      <c r="I133" t="str">
+        <v>0</v>
+      </c>
+      <c r="J133" t="str">
+        <v>3</v>
+      </c>
+      <c r="K133" t="str">
+        <v>0</v>
+      </c>
+      <c r="L133" t="str">
+        <v>1</v>
+      </c>
+      <c r="M133" t="str">
+        <v>0</v>
+      </c>
+      <c r="N133" t="str">
+        <v>4</v>
+      </c>
+      <c r="O133" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P133" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q133" t="str">
+        <v>풍덕천동732-6</v>
+      </c>
+      <c r="R133" t="str">
+        <v/>
+      </c>
+      <c r="S133" t="str">
+        <v>용인서부소방서수지119안전센터 앞 도로(풍덕천로177)</v>
+      </c>
+      <c r="T133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>26-18</v>
+      </c>
+      <c r="B134" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C134" t="str">
+        <v>26-용인시-18</v>
+      </c>
+      <c r="D134" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E134" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F134" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G134" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H134" t="str">
+        <v>-</v>
+      </c>
+      <c r="I134" t="str">
+        <v>0</v>
+      </c>
+      <c r="J134" t="str">
+        <v>3</v>
+      </c>
+      <c r="K134" t="str">
+        <v>0</v>
+      </c>
+      <c r="L134" t="str">
+        <v>1</v>
+      </c>
+      <c r="M134" t="str">
+        <v>0</v>
+      </c>
+      <c r="N134" t="str">
+        <v>4</v>
+      </c>
+      <c r="O134" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P134" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q134" t="str">
+        <v>풍덕천동703-4</v>
+      </c>
+      <c r="R134" t="str">
+        <v/>
+      </c>
+      <c r="S134" t="str">
+        <v>수지분당 공인중개사사무소 앞 도로(풍덕천로169)</v>
+      </c>
+      <c r="T134" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>26-19</v>
+      </c>
+      <c r="B135" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C135" t="str">
+        <v>26-용인시-19</v>
+      </c>
+      <c r="D135" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E135" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F135" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G135" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H135" t="str">
+        <v>-</v>
+      </c>
+      <c r="I135" t="str">
+        <v>0</v>
+      </c>
+      <c r="J135" t="str">
+        <v>3</v>
+      </c>
+      <c r="K135" t="str">
+        <v>0</v>
+      </c>
+      <c r="L135" t="str">
+        <v>1</v>
+      </c>
+      <c r="M135" t="str">
+        <v>0</v>
+      </c>
+      <c r="N135" t="str">
+        <v>4</v>
+      </c>
+      <c r="O135" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P135" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q135" t="str">
+        <v>풍덕천동703</v>
+      </c>
+      <c r="R135" t="str">
+        <v/>
+      </c>
+      <c r="S135" t="str">
+        <v>동보아파트 놀이터 앞 도로(풍덕천로155)</v>
+      </c>
+      <c r="T135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>26-20</v>
+      </c>
+      <c r="B136" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C136" t="str">
+        <v>26-용인시-20</v>
+      </c>
+      <c r="D136" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E136" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F136" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G136" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H136" t="str">
+        <v>-</v>
+      </c>
+      <c r="I136" t="str">
+        <v>0</v>
+      </c>
+      <c r="J136" t="str">
+        <v>3</v>
+      </c>
+      <c r="K136" t="str">
+        <v>0</v>
+      </c>
+      <c r="L136" t="str">
+        <v>1</v>
+      </c>
+      <c r="M136" t="str">
+        <v>0</v>
+      </c>
+      <c r="N136" t="str">
+        <v>4</v>
+      </c>
+      <c r="O136" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P136" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q136" t="str">
+        <v>풍덕천동703</v>
+      </c>
+      <c r="R136" t="str">
+        <v/>
+      </c>
+      <c r="S136" t="str">
+        <v>동보아파트 서울아파트 앞 도로(풍덕천로161)</v>
+      </c>
+      <c r="T136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>26-21</v>
+      </c>
+      <c r="B137" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C137" t="str">
+        <v>26-용인시-21</v>
+      </c>
+      <c r="D137" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E137" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F137" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G137" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H137" t="str">
+        <v>-</v>
+      </c>
+      <c r="I137" t="str">
+        <v>0</v>
+      </c>
+      <c r="J137" t="str">
+        <v>3</v>
+      </c>
+      <c r="K137" t="str">
+        <v>0</v>
+      </c>
+      <c r="L137" t="str">
+        <v>1</v>
+      </c>
+      <c r="M137" t="str">
+        <v>0</v>
+      </c>
+      <c r="N137" t="str">
+        <v>4</v>
+      </c>
+      <c r="O137" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P137" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q137" t="str">
+        <v>현대그린프라자 삼거리</v>
+      </c>
+      <c r="R137" t="str">
+        <v/>
+      </c>
+      <c r="S137" t="str">
+        <v>현대그린프라자 삼거리</v>
+      </c>
+      <c r="T137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>26-22</v>
+      </c>
+      <c r="B138" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C138" t="str">
+        <v>26-용인시-22</v>
+      </c>
+      <c r="D138" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E138" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F138" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G138" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H138" t="str">
+        <v>-</v>
+      </c>
+      <c r="I138" t="str">
+        <v>0</v>
+      </c>
+      <c r="J138" t="str">
+        <v>3</v>
+      </c>
+      <c r="K138" t="str">
+        <v>0</v>
+      </c>
+      <c r="L138" t="str">
+        <v>1</v>
+      </c>
+      <c r="M138" t="str">
+        <v>0</v>
+      </c>
+      <c r="N138" t="str">
+        <v>4</v>
+      </c>
+      <c r="O138" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P138" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q138" t="str">
+        <v>풍덕천동715-2</v>
+      </c>
+      <c r="R138" t="str">
+        <v/>
+      </c>
+      <c r="S138" t="str">
+        <v>현대그린프라자 앞 도로(풍덕천로149)</v>
+      </c>
+      <c r="T138" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T132"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T138"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-용인시-보고서.xlsx
+++ b/25-경기철도-용인시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T138"/>
+  <dimension ref="A1:T140"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9088,9 +9088,133 @@
         <v/>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>26-23</v>
+      </c>
+      <c r="B139" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C139" t="str">
+        <v>26-용인시-23</v>
+      </c>
+      <c r="D139" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E139" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F139" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G139" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H139" t="str">
+        <v>-</v>
+      </c>
+      <c r="I139" t="str">
+        <v>0</v>
+      </c>
+      <c r="J139" t="str">
+        <v>3</v>
+      </c>
+      <c r="K139" t="str">
+        <v>0</v>
+      </c>
+      <c r="L139" t="str">
+        <v>1</v>
+      </c>
+      <c r="M139" t="str">
+        <v>0</v>
+      </c>
+      <c r="N139" t="str">
+        <v>4</v>
+      </c>
+      <c r="O139" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P139" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q139" t="str">
+        <v>풍덕천동714-5</v>
+      </c>
+      <c r="R139" t="str">
+        <v/>
+      </c>
+      <c r="S139" t="str">
+        <v>버거킹_수지구청역점 앞 도로(풍덕천로145)</v>
+      </c>
+      <c r="T139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>26-24</v>
+      </c>
+      <c r="B140" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C140" t="str">
+        <v>26-용인시-24</v>
+      </c>
+      <c r="D140" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E140" t="str">
+        <v>양호</v>
+      </c>
+      <c r="F140" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G140" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H140" t="str">
+        <v>-</v>
+      </c>
+      <c r="I140" t="str">
+        <v>0</v>
+      </c>
+      <c r="J140" t="str">
+        <v>0</v>
+      </c>
+      <c r="K140" t="str">
+        <v>0</v>
+      </c>
+      <c r="L140" t="str">
+        <v>1</v>
+      </c>
+      <c r="M140" t="str">
+        <v>0</v>
+      </c>
+      <c r="N140" t="str">
+        <v>1</v>
+      </c>
+      <c r="O140" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P140" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q140" t="str">
+        <v>풍덕천동714-5</v>
+      </c>
+      <c r="R140" t="str">
+        <v/>
+      </c>
+      <c r="S140" t="str">
+        <v>버거킹_수지구청역점 앞 보도(풍덕천로145)</v>
+      </c>
+      <c r="T140" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T138"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T140"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-용인시-보고서.xlsx
+++ b/25-경기철도-용인시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T140"/>
+  <dimension ref="A1:T145"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9212,9 +9212,319 @@
         <v/>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>26-25</v>
+      </c>
+      <c r="B141" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C141" t="str">
+        <v>26-용인시-25</v>
+      </c>
+      <c r="D141" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E141" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F141" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G141" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H141" t="str">
+        <v>-</v>
+      </c>
+      <c r="I141" t="str">
+        <v>0</v>
+      </c>
+      <c r="J141" t="str">
+        <v>3</v>
+      </c>
+      <c r="K141" t="str">
+        <v>0</v>
+      </c>
+      <c r="L141" t="str">
+        <v>1</v>
+      </c>
+      <c r="M141" t="str">
+        <v>0</v>
+      </c>
+      <c r="N141" t="str">
+        <v>4</v>
+      </c>
+      <c r="O141" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P141" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q141" t="str">
+        <v>풍덕천동714-4</v>
+      </c>
+      <c r="R141" t="str">
+        <v/>
+      </c>
+      <c r="S141" t="str">
+        <v>수풍소공원 앞 도로</v>
+      </c>
+      <c r="T141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>26-26</v>
+      </c>
+      <c r="B142" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C142" t="str">
+        <v>26-용인시-26</v>
+      </c>
+      <c r="D142" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E142" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F142" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G142" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H142" t="str">
+        <v>-</v>
+      </c>
+      <c r="I142" t="str">
+        <v>0</v>
+      </c>
+      <c r="J142" t="str">
+        <v>3</v>
+      </c>
+      <c r="K142" t="str">
+        <v>0</v>
+      </c>
+      <c r="L142" t="str">
+        <v>1</v>
+      </c>
+      <c r="M142" t="str">
+        <v>0</v>
+      </c>
+      <c r="N142" t="str">
+        <v>4</v>
+      </c>
+      <c r="O142" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P142" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q142" t="str">
+        <v>풍덕천동714-4</v>
+      </c>
+      <c r="R142" t="str">
+        <v/>
+      </c>
+      <c r="S142" t="str">
+        <v>수풍소공원 앞 교차로</v>
+      </c>
+      <c r="T142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>26-27</v>
+      </c>
+      <c r="B143" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C143" t="str">
+        <v>26-용인시-27</v>
+      </c>
+      <c r="D143" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E143" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F143" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G143" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H143" t="str">
+        <v>-</v>
+      </c>
+      <c r="I143" t="str">
+        <v>0</v>
+      </c>
+      <c r="J143" t="str">
+        <v>3</v>
+      </c>
+      <c r="K143" t="str">
+        <v>0</v>
+      </c>
+      <c r="L143" t="str">
+        <v>1</v>
+      </c>
+      <c r="M143" t="str">
+        <v>0</v>
+      </c>
+      <c r="N143" t="str">
+        <v>4</v>
+      </c>
+      <c r="O143" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P143" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q143" t="str">
+        <v>풍덕천동713-5</v>
+      </c>
+      <c r="R143" t="str">
+        <v/>
+      </c>
+      <c r="S143" t="str">
+        <v>금오프라자 롯데리아 앞 도로(풍덕천로133)</v>
+      </c>
+      <c r="T143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>26-28</v>
+      </c>
+      <c r="B144" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C144" t="str">
+        <v>26-용인시-28</v>
+      </c>
+      <c r="D144" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E144" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F144" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G144" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H144" t="str">
+        <v>-</v>
+      </c>
+      <c r="I144" t="str">
+        <v>0</v>
+      </c>
+      <c r="J144" t="str">
+        <v>3</v>
+      </c>
+      <c r="K144" t="str">
+        <v>0</v>
+      </c>
+      <c r="L144" t="str">
+        <v>1</v>
+      </c>
+      <c r="M144" t="str">
+        <v>0</v>
+      </c>
+      <c r="N144" t="str">
+        <v>4</v>
+      </c>
+      <c r="O144" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P144" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q144" t="str">
+        <v>풍덕천동712-3</v>
+      </c>
+      <c r="R144" t="str">
+        <v/>
+      </c>
+      <c r="S144" t="str">
+        <v>수지프라자 하르당 앞 도로(풍덕천로127)</v>
+      </c>
+      <c r="T144" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>26-29</v>
+      </c>
+      <c r="B145" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C145" t="str">
+        <v>26-용인시-29</v>
+      </c>
+      <c r="D145" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E145" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F145" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G145" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H145" t="str">
+        <v>-</v>
+      </c>
+      <c r="I145" t="str">
+        <v>0</v>
+      </c>
+      <c r="J145" t="str">
+        <v>3</v>
+      </c>
+      <c r="K145" t="str">
+        <v>0</v>
+      </c>
+      <c r="L145" t="str">
+        <v>1</v>
+      </c>
+      <c r="M145" t="str">
+        <v>0</v>
+      </c>
+      <c r="N145" t="str">
+        <v>4</v>
+      </c>
+      <c r="O145" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P145" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q145" t="str">
+        <v>로얄스포츠센터사거리</v>
+      </c>
+      <c r="R145" t="str">
+        <v/>
+      </c>
+      <c r="S145" t="str">
+        <v>로얄스포츠센터사거리</v>
+      </c>
+      <c r="T145" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T140"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T145"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-용인시-보고서.xlsx
+++ b/25-경기철도-용인시-보고서.xlsx
@@ -8958,7 +8958,7 @@
         <v/>
       </c>
       <c r="S136" t="str">
-        <v>동보아파트 서울아파트 앞 도로(풍덕천로161)</v>
+        <v>동보아파트 서울치과의원 앞 양차선(풍덕천로161)</v>
       </c>
       <c r="T136" t="str">
         <v/>

--- a/25-경기철도-용인시-보고서.xlsx
+++ b/25-경기철도-용인시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T145"/>
+  <dimension ref="A1:T148"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9522,9 +9522,195 @@
         <v/>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>26-30</v>
+      </c>
+      <c r="B146" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C146" t="str">
+        <v>26-용인시-30</v>
+      </c>
+      <c r="D146" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E146" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F146" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G146" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H146" t="str">
+        <v>-</v>
+      </c>
+      <c r="I146" t="str">
+        <v>0</v>
+      </c>
+      <c r="J146" t="str">
+        <v>3</v>
+      </c>
+      <c r="K146" t="str">
+        <v>0</v>
+      </c>
+      <c r="L146" t="str">
+        <v>1</v>
+      </c>
+      <c r="M146" t="str">
+        <v>0</v>
+      </c>
+      <c r="N146" t="str">
+        <v>4</v>
+      </c>
+      <c r="O146" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P146" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q146" t="str">
+        <v>풍덕천동1065</v>
+      </c>
+      <c r="R146" t="str">
+        <v/>
+      </c>
+      <c r="S146" t="str">
+        <v>주공1단지 아파트 102동 앞 도로(풍덕천로91)5cm이하 침하</v>
+      </c>
+      <c r="T146" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>26-31</v>
+      </c>
+      <c r="B147" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C147" t="str">
+        <v>26-용인시-31</v>
+      </c>
+      <c r="D147" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E147" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F147" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G147" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H147" t="str">
+        <v>-</v>
+      </c>
+      <c r="I147" t="str">
+        <v>0</v>
+      </c>
+      <c r="J147" t="str">
+        <v>3</v>
+      </c>
+      <c r="K147" t="str">
+        <v>0</v>
+      </c>
+      <c r="L147" t="str">
+        <v>1</v>
+      </c>
+      <c r="M147" t="str">
+        <v>0</v>
+      </c>
+      <c r="N147" t="str">
+        <v>4</v>
+      </c>
+      <c r="O147" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P147" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q147" t="str">
+        <v>풍덕천동1097</v>
+      </c>
+      <c r="R147" t="str">
+        <v/>
+      </c>
+      <c r="S147" t="str">
+        <v>신정마을 정문 앞 도로(풍덕천로86)</v>
+      </c>
+      <c r="T147" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>26-32</v>
+      </c>
+      <c r="B148" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C148" t="str">
+        <v>26-용인시-32</v>
+      </c>
+      <c r="D148" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E148" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F148" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G148" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H148" t="str">
+        <v>-</v>
+      </c>
+      <c r="I148" t="str">
+        <v>0</v>
+      </c>
+      <c r="J148" t="str">
+        <v>3</v>
+      </c>
+      <c r="K148" t="str">
+        <v>0</v>
+      </c>
+      <c r="L148" t="str">
+        <v>1</v>
+      </c>
+      <c r="M148" t="str">
+        <v>0</v>
+      </c>
+      <c r="N148" t="str">
+        <v>4</v>
+      </c>
+      <c r="O148" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P148" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q148" t="str">
+        <v>풍덕천동1065-2</v>
+      </c>
+      <c r="R148" t="str">
+        <v/>
+      </c>
+      <c r="S148" t="str">
+        <v>GS25 앞 양차선(풍덕천로89)</v>
+      </c>
+      <c r="T148" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T145"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T148"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-용인시-보고서.xlsx
+++ b/25-경기철도-용인시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T148"/>
+  <dimension ref="A1:T153"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9708,9 +9708,319 @@
         <v>현장확인필요</v>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>26-33</v>
+      </c>
+      <c r="B149" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C149" t="str">
+        <v>26-용인시-33</v>
+      </c>
+      <c r="D149" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E149" t="str">
+        <v>횡균열</v>
+      </c>
+      <c r="F149" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G149" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H149" t="str">
+        <v>-</v>
+      </c>
+      <c r="I149" t="str">
+        <v>0</v>
+      </c>
+      <c r="J149" t="str">
+        <v>1</v>
+      </c>
+      <c r="K149" t="str">
+        <v>0</v>
+      </c>
+      <c r="L149" t="str">
+        <v>1</v>
+      </c>
+      <c r="M149" t="str">
+        <v>0</v>
+      </c>
+      <c r="N149" t="str">
+        <v>2</v>
+      </c>
+      <c r="O149" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P149" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q149" t="str">
+        <v>풍덕천동1064</v>
+      </c>
+      <c r="R149" t="str">
+        <v/>
+      </c>
+      <c r="S149" t="str">
+        <v>믿음공인중개사 사무소 앞 도로(풍덕천로89)</v>
+      </c>
+      <c r="T149" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>26-34</v>
+      </c>
+      <c r="B150" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C150" t="str">
+        <v>26-용인시-34</v>
+      </c>
+      <c r="D150" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E150" t="str">
+        <v>양호</v>
+      </c>
+      <c r="F150" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G150" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H150" t="str">
+        <v>-</v>
+      </c>
+      <c r="I150" t="str">
+        <v>0</v>
+      </c>
+      <c r="J150" t="str">
+        <v>1</v>
+      </c>
+      <c r="K150" t="str">
+        <v>0</v>
+      </c>
+      <c r="L150" t="str">
+        <v>1</v>
+      </c>
+      <c r="M150" t="str">
+        <v>0</v>
+      </c>
+      <c r="N150" t="str">
+        <v>2</v>
+      </c>
+      <c r="O150" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P150" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q150" t="str">
+        <v>풍덕천동1060</v>
+      </c>
+      <c r="R150" t="str">
+        <v/>
+      </c>
+      <c r="S150" t="str">
+        <v>상록아파트 정문 앞 도로(풍덕천로75)</v>
+      </c>
+      <c r="T150" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>26-35</v>
+      </c>
+      <c r="B151" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C151" t="str">
+        <v>26-용인시-35</v>
+      </c>
+      <c r="D151" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E151" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F151" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G151" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H151" t="str">
+        <v>-</v>
+      </c>
+      <c r="I151" t="str">
+        <v>0</v>
+      </c>
+      <c r="J151" t="str">
+        <v>3</v>
+      </c>
+      <c r="K151" t="str">
+        <v>0</v>
+      </c>
+      <c r="L151" t="str">
+        <v>1</v>
+      </c>
+      <c r="M151" t="str">
+        <v>0</v>
+      </c>
+      <c r="N151" t="str">
+        <v>4</v>
+      </c>
+      <c r="O151" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P151" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q151" t="str">
+        <v>풍덕천동1051-2</v>
+      </c>
+      <c r="R151" t="str">
+        <v/>
+      </c>
+      <c r="S151" t="str">
+        <v>풍덕천2동행정복지센터 앞 양차선(풍덕천로51)</v>
+      </c>
+      <c r="T151" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>26-36</v>
+      </c>
+      <c r="B152" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C152" t="str">
+        <v>26-용인시-36</v>
+      </c>
+      <c r="D152" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E152" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F152" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G152" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H152" t="str">
+        <v>-</v>
+      </c>
+      <c r="I152" t="str">
+        <v>0</v>
+      </c>
+      <c r="J152" t="str">
+        <v>3</v>
+      </c>
+      <c r="K152" t="str">
+        <v>0</v>
+      </c>
+      <c r="L152" t="str">
+        <v>1</v>
+      </c>
+      <c r="M152" t="str">
+        <v>0</v>
+      </c>
+      <c r="N152" t="str">
+        <v>4</v>
+      </c>
+      <c r="O152" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P152" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q152" t="str">
+        <v>풍덕천동1051-1</v>
+      </c>
+      <c r="R152" t="str">
+        <v/>
+      </c>
+      <c r="S152" t="str">
+        <v>즐거운한우_수지 앞 도로(정평로34-2)</v>
+      </c>
+      <c r="T152" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>26-37</v>
+      </c>
+      <c r="B153" t="str">
+        <v>풍덕천로</v>
+      </c>
+      <c r="C153" t="str">
+        <v>26-용인시-37</v>
+      </c>
+      <c r="D153" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E153" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F153" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G153" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H153" t="str">
+        <v>-</v>
+      </c>
+      <c r="I153" t="str">
+        <v>0</v>
+      </c>
+      <c r="J153" t="str">
+        <v>3</v>
+      </c>
+      <c r="K153" t="str">
+        <v>0</v>
+      </c>
+      <c r="L153" t="str">
+        <v>1</v>
+      </c>
+      <c r="M153" t="str">
+        <v>0</v>
+      </c>
+      <c r="N153" t="str">
+        <v>4</v>
+      </c>
+      <c r="O153" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P153" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q153" t="str">
+        <v>정평중학교사거리</v>
+      </c>
+      <c r="R153" t="str">
+        <v/>
+      </c>
+      <c r="S153" t="str">
+        <v>정평중학교사거리</v>
+      </c>
+      <c r="T153" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T148"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T153"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-용인시-보고서.xlsx
+++ b/25-경기철도-용인시-보고서.xlsx
@@ -9581,7 +9581,7 @@
         <v>주공1단지 아파트 102동 앞 도로(풍덕천로91)5cm이하 침하</v>
       </c>
       <c r="T146" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="147">
@@ -9643,7 +9643,7 @@
         <v>신정마을 정문 앞 도로(풍덕천로86)</v>
       </c>
       <c r="T147" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="148">
@@ -9705,7 +9705,7 @@
         <v>GS25 앞 양차선(풍덕천로89)</v>
       </c>
       <c r="T148" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="149">
@@ -9767,7 +9767,7 @@
         <v>믿음공인중개사 사무소 앞 도로(풍덕천로89)</v>
       </c>
       <c r="T149" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="150">
@@ -9829,7 +9829,7 @@
         <v>상록아파트 정문 앞 도로(풍덕천로75)</v>
       </c>
       <c r="T150" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="151">
@@ -9891,7 +9891,7 @@
         <v>풍덕천2동행정복지센터 앞 양차선(풍덕천로51)</v>
       </c>
       <c r="T151" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="152">
@@ -9953,7 +9953,7 @@
         <v>즐거운한우_수지 앞 도로(정평로34-2)</v>
       </c>
       <c r="T152" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="153">
@@ -10015,7 +10015,7 @@
         <v>정평중학교사거리</v>
       </c>
       <c r="T153" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/25-경기철도-용인시-보고서.xlsx
+++ b/25-경기철도-용인시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T155"/>
+  <dimension ref="A1:T159"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10140,9 +10140,257 @@
         <v/>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>26-41</v>
+      </c>
+      <c r="B156" t="str">
+        <v>수지로</v>
+      </c>
+      <c r="C156" t="str">
+        <v>26-용인시-41</v>
+      </c>
+      <c r="D156" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E156" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F156" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G156" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H156" t="str">
+        <v>-</v>
+      </c>
+      <c r="I156" t="str">
+        <v>0</v>
+      </c>
+      <c r="J156" t="str">
+        <v>3</v>
+      </c>
+      <c r="K156" t="str">
+        <v>0</v>
+      </c>
+      <c r="L156" t="str">
+        <v>1</v>
+      </c>
+      <c r="M156" t="str">
+        <v>0</v>
+      </c>
+      <c r="N156" t="str">
+        <v>4</v>
+      </c>
+      <c r="O156" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P156" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q156" t="str">
+        <v>성복동740</v>
+      </c>
+      <c r="R156" t="str">
+        <v/>
+      </c>
+      <c r="S156" t="str">
+        <v>드림타워 버스정류장 앞 도로(성복2로76번길26-3)</v>
+      </c>
+      <c r="T156" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>26-42</v>
+      </c>
+      <c r="B157" t="str">
+        <v>수지로</v>
+      </c>
+      <c r="C157" t="str">
+        <v>26-용인시-42</v>
+      </c>
+      <c r="D157" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E157" t="str">
+        <v>종횡균열</v>
+      </c>
+      <c r="F157" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G157" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H157" t="str">
+        <v>-</v>
+      </c>
+      <c r="I157" t="str">
+        <v>0</v>
+      </c>
+      <c r="J157" t="str">
+        <v>1</v>
+      </c>
+      <c r="K157" t="str">
+        <v>0</v>
+      </c>
+      <c r="L157" t="str">
+        <v>1</v>
+      </c>
+      <c r="M157" t="str">
+        <v>0</v>
+      </c>
+      <c r="N157" t="str">
+        <v>2</v>
+      </c>
+      <c r="O157" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P157" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q157" t="str">
+        <v>푸른마을 푸르지오삼거리</v>
+      </c>
+      <c r="R157" t="str">
+        <v/>
+      </c>
+      <c r="S157" t="str">
+        <v>푸르지오삼거리(성복2로76번길26-3)</v>
+      </c>
+      <c r="T157" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>26-43</v>
+      </c>
+      <c r="B158" t="str">
+        <v>수지로</v>
+      </c>
+      <c r="C158" t="str">
+        <v>26-용인시-43</v>
+      </c>
+      <c r="D158" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E158" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F158" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G158" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H158" t="str">
+        <v>-</v>
+      </c>
+      <c r="I158" t="str">
+        <v>0</v>
+      </c>
+      <c r="J158" t="str">
+        <v>3</v>
+      </c>
+      <c r="K158" t="str">
+        <v>0</v>
+      </c>
+      <c r="L158" t="str">
+        <v>1</v>
+      </c>
+      <c r="M158" t="str">
+        <v>0</v>
+      </c>
+      <c r="N158" t="str">
+        <v>4</v>
+      </c>
+      <c r="O158" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P158" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q158" t="str">
+        <v>성복동748-2</v>
+      </c>
+      <c r="R158" t="str">
+        <v/>
+      </c>
+      <c r="S158" t="str">
+        <v>신봉샤르망1 정관장 앞 도로(성복2로76번길26-6)</v>
+      </c>
+      <c r="T158" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>26-44</v>
+      </c>
+      <c r="B159" t="str">
+        <v>수지로</v>
+      </c>
+      <c r="C159" t="str">
+        <v>26-용인시-44</v>
+      </c>
+      <c r="D159" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E159" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F159" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G159" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H159" t="str">
+        <v>-</v>
+      </c>
+      <c r="I159" t="str">
+        <v>0</v>
+      </c>
+      <c r="J159" t="str">
+        <v>3</v>
+      </c>
+      <c r="K159" t="str">
+        <v>0</v>
+      </c>
+      <c r="L159" t="str">
+        <v>1</v>
+      </c>
+      <c r="M159" t="str">
+        <v>0</v>
+      </c>
+      <c r="N159" t="str">
+        <v>4</v>
+      </c>
+      <c r="O159" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P159" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q159" t="str">
+        <v>풍덕천동607-48</v>
+      </c>
+      <c r="R159" t="str">
+        <v/>
+      </c>
+      <c r="S159" t="str">
+        <v>어청교 앞 양차선</v>
+      </c>
+      <c r="T159" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T155"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T159"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-용인시-보고서.xlsx
+++ b/25-경기철도-용인시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T159"/>
+  <dimension ref="A1:T161"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10388,9 +10388,133 @@
         <v/>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>26-45</v>
+      </c>
+      <c r="B160" t="str">
+        <v>수지로</v>
+      </c>
+      <c r="C160" t="str">
+        <v>26-용인시-45</v>
+      </c>
+      <c r="D160" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E160" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F160" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G160" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H160" t="str">
+        <v>-</v>
+      </c>
+      <c r="I160" t="str">
+        <v>0</v>
+      </c>
+      <c r="J160" t="str">
+        <v>3</v>
+      </c>
+      <c r="K160" t="str">
+        <v>0</v>
+      </c>
+      <c r="L160" t="str">
+        <v>1</v>
+      </c>
+      <c r="M160" t="str">
+        <v>0</v>
+      </c>
+      <c r="N160" t="str">
+        <v>4</v>
+      </c>
+      <c r="O160" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P160" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q160" t="str">
+        <v>성복동입구 교차로</v>
+      </c>
+      <c r="R160" t="str">
+        <v/>
+      </c>
+      <c r="S160" t="str">
+        <v>성복동입구 교차로</v>
+      </c>
+      <c r="T160" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>26-46</v>
+      </c>
+      <c r="B161" t="str">
+        <v>수지로</v>
+      </c>
+      <c r="C161" t="str">
+        <v>26-용인시-46</v>
+      </c>
+      <c r="D161" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E161" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F161" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G161" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H161" t="str">
+        <v>-</v>
+      </c>
+      <c r="I161" t="str">
+        <v>0</v>
+      </c>
+      <c r="J161" t="str">
+        <v>3</v>
+      </c>
+      <c r="K161" t="str">
+        <v>0</v>
+      </c>
+      <c r="L161" t="str">
+        <v>1</v>
+      </c>
+      <c r="M161" t="str">
+        <v>0</v>
+      </c>
+      <c r="N161" t="str">
+        <v>4</v>
+      </c>
+      <c r="O161" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P161" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q161" t="str">
+        <v>수지구 성복동69-1</v>
+      </c>
+      <c r="R161" t="str">
+        <v/>
+      </c>
+      <c r="S161" t="str">
+        <v>성복제일교회 앞 도로(수지로113)</v>
+      </c>
+      <c r="T161" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T159"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T161"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-용인시-보고서.xlsx
+++ b/25-경기철도-용인시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T161"/>
+  <dimension ref="A1:T164"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10512,9 +10512,195 @@
         <v/>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>26-47</v>
+      </c>
+      <c r="B162" t="str">
+        <v>수지로</v>
+      </c>
+      <c r="C162" t="str">
+        <v>26-용인시-47</v>
+      </c>
+      <c r="D162" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E162" t="str">
+        <v>종균열</v>
+      </c>
+      <c r="F162" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G162" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H162" t="str">
+        <v>-</v>
+      </c>
+      <c r="I162" t="str">
+        <v>0</v>
+      </c>
+      <c r="J162" t="str">
+        <v>1</v>
+      </c>
+      <c r="K162" t="str">
+        <v>0</v>
+      </c>
+      <c r="L162" t="str">
+        <v>1</v>
+      </c>
+      <c r="M162" t="str">
+        <v>0</v>
+      </c>
+      <c r="N162" t="str">
+        <v>2</v>
+      </c>
+      <c r="O162" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P162" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q162" t="str">
+        <v>성복동90</v>
+      </c>
+      <c r="R162" t="str">
+        <v/>
+      </c>
+      <c r="S162" t="str">
+        <v>성동마을엘지빌리지2차아파트 202동 앞 도로(수지로113번길15)</v>
+      </c>
+      <c r="T162" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>26-48</v>
+      </c>
+      <c r="B163" t="str">
+        <v>수지로</v>
+      </c>
+      <c r="C163" t="str">
+        <v>26-용인시-48</v>
+      </c>
+      <c r="D163" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E163" t="str">
+        <v>양호</v>
+      </c>
+      <c r="F163" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G163" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H163" t="str">
+        <v>-</v>
+      </c>
+      <c r="I163" t="str">
+        <v>-</v>
+      </c>
+      <c r="J163" t="str">
+        <v>0</v>
+      </c>
+      <c r="K163" t="str">
+        <v>0</v>
+      </c>
+      <c r="L163" t="str">
+        <v>1</v>
+      </c>
+      <c r="M163" t="str">
+        <v>0</v>
+      </c>
+      <c r="N163" t="str">
+        <v>-</v>
+      </c>
+      <c r="O163" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P163" t="str">
+        <v>cm 침하</v>
+      </c>
+      <c r="Q163" t="str">
+        <v>상현동105-1</v>
+      </c>
+      <c r="R163" t="str">
+        <v/>
+      </c>
+      <c r="S163" t="str">
+        <v>저먼오토 앞 도로(수지로88)</v>
+      </c>
+      <c r="T163" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>26-49</v>
+      </c>
+      <c r="B164" t="str">
+        <v>수지로</v>
+      </c>
+      <c r="C164" t="str">
+        <v>26-용인시-49</v>
+      </c>
+      <c r="D164" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E164" t="str">
+        <v>종횡균열</v>
+      </c>
+      <c r="F164" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G164" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H164" t="str">
+        <v>-</v>
+      </c>
+      <c r="I164" t="str">
+        <v>0</v>
+      </c>
+      <c r="J164" t="str">
+        <v>1</v>
+      </c>
+      <c r="K164" t="str">
+        <v>0</v>
+      </c>
+      <c r="L164" t="str">
+        <v>1</v>
+      </c>
+      <c r="M164" t="str">
+        <v>0</v>
+      </c>
+      <c r="N164" t="str">
+        <v>2</v>
+      </c>
+      <c r="O164" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P164" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q164" t="str">
+        <v>성복동814</v>
+      </c>
+      <c r="R164" t="str">
+        <v/>
+      </c>
+      <c r="S164" t="str">
+        <v>롯데캐슬 파크나인 신한은행 앞 도로(성복1로13)</v>
+      </c>
+      <c r="T164" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T161"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T164"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-용인시-보고서.xlsx
+++ b/25-경기철도-용인시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T178"/>
+  <dimension ref="A1:T183"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11564,9 +11564,319 @@
         <v/>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>26-65</v>
+      </c>
+      <c r="B179" t="str">
+        <v>광교중앙로</v>
+      </c>
+      <c r="C179" t="str">
+        <v>26-용인시-65</v>
+      </c>
+      <c r="D179" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E179" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F179" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G179" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H179" t="str">
+        <v>-</v>
+      </c>
+      <c r="I179" t="str">
+        <v>0</v>
+      </c>
+      <c r="J179" t="str">
+        <v>3</v>
+      </c>
+      <c r="K179" t="str">
+        <v>0</v>
+      </c>
+      <c r="L179" t="str">
+        <v>1</v>
+      </c>
+      <c r="M179" t="str">
+        <v>0</v>
+      </c>
+      <c r="N179" t="str">
+        <v>4</v>
+      </c>
+      <c r="O179" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P179" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q179" t="str">
+        <v>상현동1117-3</v>
+      </c>
+      <c r="R179" t="str">
+        <v/>
+      </c>
+      <c r="S179" t="str">
+        <v>희성빌딩 KT프라자 앞 도로(광교중앙로311)</v>
+      </c>
+      <c r="T179" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>26-66</v>
+      </c>
+      <c r="B180" t="str">
+        <v>광교중앙로</v>
+      </c>
+      <c r="C180" t="str">
+        <v>26-용인시-66</v>
+      </c>
+      <c r="D180" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E180" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F180" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G180" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H180" t="str">
+        <v>-</v>
+      </c>
+      <c r="I180" t="str">
+        <v>0</v>
+      </c>
+      <c r="J180" t="str">
+        <v>3</v>
+      </c>
+      <c r="K180" t="str">
+        <v>0</v>
+      </c>
+      <c r="L180" t="str">
+        <v>1</v>
+      </c>
+      <c r="M180" t="str">
+        <v>0</v>
+      </c>
+      <c r="N180" t="str">
+        <v>4</v>
+      </c>
+      <c r="O180" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P180" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q180" t="str">
+        <v>상현동1117-5</v>
+      </c>
+      <c r="R180" t="str">
+        <v/>
+      </c>
+      <c r="S180" t="str">
+        <v>광교2차푸르지오시티C동오피스텔 행복부동산 앞 도로(광교중앙로305)</v>
+      </c>
+      <c r="T180" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>26-67</v>
+      </c>
+      <c r="B181" t="str">
+        <v>광교중앙로</v>
+      </c>
+      <c r="C181" t="str">
+        <v>26-용인시-67</v>
+      </c>
+      <c r="D181" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E181" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F181" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G181" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H181" t="str">
+        <v>-</v>
+      </c>
+      <c r="I181" t="str">
+        <v>0</v>
+      </c>
+      <c r="J181" t="str">
+        <v>0</v>
+      </c>
+      <c r="K181" t="str">
+        <v>0</v>
+      </c>
+      <c r="L181" t="str">
+        <v>1</v>
+      </c>
+      <c r="M181" t="str">
+        <v>0</v>
+      </c>
+      <c r="N181" t="str">
+        <v>1</v>
+      </c>
+      <c r="O181" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P181" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q181" t="str">
+        <v>상현동1117-5</v>
+      </c>
+      <c r="R181" t="str">
+        <v/>
+      </c>
+      <c r="S181" t="str">
+        <v>광교2차푸르지오시티C동오피스텔 서브웨이 앞 도로(광교중앙로305)</v>
+      </c>
+      <c r="T181" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>26-68</v>
+      </c>
+      <c r="B182" t="str">
+        <v>광교중앙로</v>
+      </c>
+      <c r="C182" t="str">
+        <v>26-용인시-68</v>
+      </c>
+      <c r="D182" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E182" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F182" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G182" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H182" t="str">
+        <v>-</v>
+      </c>
+      <c r="I182" t="str">
+        <v>0</v>
+      </c>
+      <c r="J182" t="str">
+        <v>3</v>
+      </c>
+      <c r="K182" t="str">
+        <v>0</v>
+      </c>
+      <c r="L182" t="str">
+        <v>1</v>
+      </c>
+      <c r="M182" t="str">
+        <v>0</v>
+      </c>
+      <c r="N182" t="str">
+        <v>4</v>
+      </c>
+      <c r="O182" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P182" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q182" t="str">
+        <v>상현동1131-6</v>
+      </c>
+      <c r="R182" t="str">
+        <v/>
+      </c>
+      <c r="S182" t="str">
+        <v>미주프라자 / #2번출구 앞 도로(광교중앙로304)</v>
+      </c>
+      <c r="T182" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>26-69</v>
+      </c>
+      <c r="B183" t="str">
+        <v>광교중앙로</v>
+      </c>
+      <c r="C183" t="str">
+        <v>26-용인시-69</v>
+      </c>
+      <c r="D183" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E183" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F183" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G183" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H183" t="str">
+        <v>-</v>
+      </c>
+      <c r="I183" t="str">
+        <v>0</v>
+      </c>
+      <c r="J183" t="str">
+        <v>3</v>
+      </c>
+      <c r="K183" t="str">
+        <v>0</v>
+      </c>
+      <c r="L183" t="str">
+        <v>1</v>
+      </c>
+      <c r="M183" t="str">
+        <v>0</v>
+      </c>
+      <c r="N183" t="str">
+        <v>4</v>
+      </c>
+      <c r="O183" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P183" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q183" t="str">
+        <v>상현동1131-8</v>
+      </c>
+      <c r="R183" t="str">
+        <v/>
+      </c>
+      <c r="S183" t="str">
+        <v>드림타워2 휴대폰도매센타-광교상현점 앞 도로(광교중앙로298)</v>
+      </c>
+      <c r="T183" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T178"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T183"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-용인시-보고서.xlsx
+++ b/25-경기철도-용인시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T183"/>
+  <dimension ref="A1:T186"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11871,12 +11871,198 @@
         <v>드림타워2 휴대폰도매센타-광교상현점 앞 도로(광교중앙로298)</v>
       </c>
       <c r="T183" t="str">
-        <v>현장확인필요</v>
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>26-70</v>
+      </c>
+      <c r="B184" t="str">
+        <v>광교중앙로</v>
+      </c>
+      <c r="C184" t="str">
+        <v>26-용인시-70</v>
+      </c>
+      <c r="D184" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E184" t="str">
+        <v>양호</v>
+      </c>
+      <c r="F184" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G184" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H184" t="str">
+        <v>-</v>
+      </c>
+      <c r="I184" t="str">
+        <v>0</v>
+      </c>
+      <c r="J184" t="str">
+        <v>3</v>
+      </c>
+      <c r="K184" t="str">
+        <v>0</v>
+      </c>
+      <c r="L184" t="str">
+        <v>1</v>
+      </c>
+      <c r="M184" t="str">
+        <v>0</v>
+      </c>
+      <c r="N184" t="str">
+        <v>4</v>
+      </c>
+      <c r="O184" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P184" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q184" t="str">
+        <v>상현동1133</v>
+      </c>
+      <c r="R184" t="str">
+        <v/>
+      </c>
+      <c r="S184" t="str">
+        <v>엘리치안오피스텔 새미케이크 앞 도로(광교중앙로294)</v>
+      </c>
+      <c r="T184" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>26-71</v>
+      </c>
+      <c r="B185" t="str">
+        <v>광교중앙로</v>
+      </c>
+      <c r="C185" t="str">
+        <v>26-용인시-71</v>
+      </c>
+      <c r="D185" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E185" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F185" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G185" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H185" t="str">
+        <v>-</v>
+      </c>
+      <c r="I185" t="str">
+        <v>0</v>
+      </c>
+      <c r="J185" t="str">
+        <v>3</v>
+      </c>
+      <c r="K185" t="str">
+        <v>0</v>
+      </c>
+      <c r="L185" t="str">
+        <v>1</v>
+      </c>
+      <c r="M185" t="str">
+        <v>0</v>
+      </c>
+      <c r="N185" t="str">
+        <v>4</v>
+      </c>
+      <c r="O185" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P185" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q185" t="str">
+        <v>광교마을사거리</v>
+      </c>
+      <c r="R185" t="str">
+        <v/>
+      </c>
+      <c r="S185" t="str">
+        <v>광교마을사거리</v>
+      </c>
+      <c r="T185" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>26-72</v>
+      </c>
+      <c r="B186" t="str">
+        <v>광교중앙로</v>
+      </c>
+      <c r="C186" t="str">
+        <v>26-용인시-72</v>
+      </c>
+      <c r="D186" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E186" t="str">
+        <v>종균열</v>
+      </c>
+      <c r="F186" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G186" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H186" t="str">
+        <v>-</v>
+      </c>
+      <c r="I186" t="str">
+        <v>0</v>
+      </c>
+      <c r="J186" t="str">
+        <v>1</v>
+      </c>
+      <c r="K186" t="str">
+        <v>0</v>
+      </c>
+      <c r="L186" t="str">
+        <v>1</v>
+      </c>
+      <c r="M186" t="str">
+        <v>0</v>
+      </c>
+      <c r="N186" t="str">
+        <v>2</v>
+      </c>
+      <c r="O186" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P186" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q186" t="str">
+        <v>상현동1066</v>
+      </c>
+      <c r="R186" t="str">
+        <v/>
+      </c>
+      <c r="S186" t="str">
+        <v>진고개통로</v>
+      </c>
+      <c r="T186" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T183"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T186"/>
   </ignoredErrors>
 </worksheet>
 </file>